--- a/backend/model/test-bill/test_bill_short_headers.xlsx
+++ b/backend/model/test-bill/test_bill_short_headers.xlsx
@@ -1,78 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ใบกำกับสินค้า" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>qty</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>SPK-NGK-R</t>
-  </si>
-  <si>
-    <t>BKP-HON-CIV</t>
-  </si>
-  <si>
-    <t>OIL-SYN-5L</t>
-  </si>
-  <si>
-    <t>Spark Plug NGK Laser Iridium</t>
-  </si>
-  <si>
-    <t>Brake Pads Front Honda Civic</t>
-  </si>
-  <si>
-    <t>Fully Synthetic Motor Oil 5L</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -84,35 +59,96 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,67 +436,522 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ใบนำเข้าสินค้า / PURCHASE INVOICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อบริษัท (TH)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>บริษัท สยามอะไหล่ยนต์ จำกัด (มหาชน)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อบริษัท (EN)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Siam Auto Parts PCL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อย่อ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>สยามอะไหล่</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ที่อยู่</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>88/8 นิคมอุตสาหกรรมบางปู ซอย 7 สมุทรปราการ 10280</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>เบอร์โทรฝ่ายขาย</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>02-324-7890</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Line ฝ่ายขาย</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>@siamparts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>อีเมลฝ่ายขาย</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>orders@siamparts.co.th</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>เลขที่บิล</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SI-2025-00231</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>วันที่รับสินค้า</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ครบกำหนดชำระ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>เครดิต</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30 วัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ขนส่งโดย</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>รถบริษัท</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>qty</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>net amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>SPK-NGK-R</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>หัวเทียน NGK Laser Iridium BKR6EIX Toyota/Honda</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="H18" s="4" t="n">
+        <v>25600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>BKP-HON-CIV</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>ผ้าเบรกหน้า Honda Civic FD 2006-2011</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>ชุด</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>OIL-SYN-5L</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>น้ำมันเครื่อง Mobil 1 Fully Synthetic 5W-30 (5L)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>ขวด</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>FLT-OIL-TOY</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>กรองน้ำมันเครื่อง Toyota 1ZZ/2ZZ/3ZZ</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>FLT-FUEL-ISZ</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>กรองน้ำมันเชื้อเพลิง Isuzu D-Max 3.0 VGS</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>ชิ้น</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>BLT-SERP-HON</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>สายพาน Serpentine Honda Accord G7 2.4</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>เส้น</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>8750</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C2">
-        <v>80</v>
-      </c>
-      <c r="D2">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>LAMP-H4-LED</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>หลอดไฟหน้า LED H4 Hi/Lo 6000K 55W (คู่)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>คู่</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C3">
-        <v>15</v>
-      </c>
-      <c r="D3">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>1450</v>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>SHK-MONO-MITS</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>โช้คอัพหลัง Mitsubishi Triton 2006-2014</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>ต้น</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2800</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>182750</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>VAT 7%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>12792.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>ยอดรวมสุทธิ</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>195542.5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>